--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -406,6 +406,15 @@
       <c r="C1" t="str">
         <v>epoch</v>
       </c>
+      <c r="D1" t="str">
+        <v>m</v>
+      </c>
+      <c r="E1" t="str">
+        <v>n</v>
+      </c>
+      <c r="F1" t="str">
+        <v>positionembedding</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -414,10 +423,53 @@
       <c r="B2" t="str">
         <v>0.000422360491938889</v>
       </c>
+      <c r="C2" t="str">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>exp1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>0.001614597043953836</v>
+      </c>
+      <c r="C3" t="str">
+        <v>90</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2</v>
+      </c>
+      <c r="F3" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>exp2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>0.0019393311813473701</v>
+      </c>
+      <c r="C4" t="str">
+        <v>90</v>
+      </c>
+      <c r="D4" t="str">
+        <v>1</v>
+      </c>
+      <c r="E4" t="str">
+        <v>1</v>
+      </c>
+      <c r="F4" t="str">
+        <v>None</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -467,9 +467,27 @@
         <v>None</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>exp3</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2.8530401323223487e-05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -474,10 +474,37 @@
       <c r="B5" t="str">
         <v>2.8530401323223487e-05</v>
       </c>
+      <c r="C5" t="str">
+        <v>90</v>
+      </c>
+      <c r="D5" t="str">
+        <v>8</v>
+      </c>
+      <c r="E5" t="str">
+        <v>8</v>
+      </c>
+      <c r="F5" t="str">
+        <v>None</v>
+      </c>
     </row>
     <row r="6">
+      <c r="A6" t="str">
+        <v>Baseline1</v>
+      </c>
       <c r="B6" t="str">
-        <v/>
+        <v>0.0004074360185768455</v>
+      </c>
+      <c r="C6" t="str">
+        <v>90</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2</v>
+      </c>
+      <c r="F6" t="str">
+        <v>None</v>
       </c>
     </row>
     <row r="7">

--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -508,8 +508,23 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="str">
+        <v>exp4</v>
+      </c>
       <c r="B7" t="str">
-        <v/>
+        <v>0.0001579983945703134</v>
+      </c>
+      <c r="C7" t="str">
+        <v>90</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2</v>
+      </c>
+      <c r="E7" t="str">
+        <v>2</v>
+      </c>
+      <c r="F7" t="str">
+        <v>None</v>
       </c>
     </row>
   </sheetData>

--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -527,9 +527,31 @@
         <v>None</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>exp5</v>
+      </c>
+      <c r="C8" t="str">
+        <v>90</v>
+      </c>
+      <c r="D8" t="str">
+        <v>4</v>
+      </c>
+      <c r="E8" t="str">
+        <v>4</v>
+      </c>
+      <c r="F8" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -531,6 +531,9 @@
       <c r="A8" t="str">
         <v>exp5</v>
       </c>
+      <c r="B8" t="str">
+        <v>6.45554464426823e-05</v>
+      </c>
       <c r="C8" t="str">
         <v>90</v>
       </c>
@@ -541,6 +544,26 @@
         <v>4</v>
       </c>
       <c r="F8" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>exp6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>0.0002967970503959805</v>
+      </c>
+      <c r="C9" t="str">
+        <v>90</v>
+      </c>
+      <c r="D9" t="str">
+        <v>4</v>
+      </c>
+      <c r="E9" t="str">
+        <v>4</v>
+      </c>
+      <c r="F9" t="str">
         <v>None</v>
       </c>
     </row>

--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -568,8 +568,23 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="str">
+        <v>exp7</v>
+      </c>
       <c r="B10" t="str">
-        <v/>
+        <v xml:space="preserve"> 6.603846850339323e-05</v>
+      </c>
+      <c r="C10" t="str">
+        <v>90</v>
+      </c>
+      <c r="D10" t="str">
+        <v>4</v>
+      </c>
+      <c r="E10" t="str">
+        <v>4</v>
+      </c>
+      <c r="F10" t="str">
+        <v>None</v>
       </c>
     </row>
   </sheetData>

--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:H11"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -415,6 +415,12 @@
       <c r="F1" t="str">
         <v>positionembedding</v>
       </c>
+      <c r="G1" t="str">
+        <v>显存</v>
+      </c>
+      <c r="H1" t="str">
+        <v>batch</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -584,12 +590,35 @@
         <v>4</v>
       </c>
       <c r="F10" t="str">
-        <v>None</v>
+        <v>leanable_mixed_rope</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>exp7</v>
+      </c>
+      <c r="C11" t="str">
+        <v>90</v>
+      </c>
+      <c r="D11" t="str">
+        <v>4</v>
+      </c>
+      <c r="E11" t="str">
+        <v>4</v>
+      </c>
+      <c r="F11" t="str">
+        <v>emded_learnable_mix_rope</v>
+      </c>
+      <c r="G11" t="str">
+        <v>16200</v>
+      </c>
+      <c r="H11" t="str">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -595,7 +595,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>exp7</v>
+        <v>exp8</v>
+      </c>
+      <c r="B11" t="str">
+        <v>6.929560186108574e-05</v>
       </c>
       <c r="C11" t="str">
         <v>90</v>
@@ -616,9 +619,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>exp9</v>
+      </c>
+      <c r="C12" t="str">
+        <v>90</v>
+      </c>
+      <c r="D12" t="str">
+        <v>4</v>
+      </c>
+      <c r="E12" t="str">
+        <v>4</v>
+      </c>
+      <c r="H12" t="str">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -623,6 +623,9 @@
       <c r="A12" t="str">
         <v>exp9</v>
       </c>
+      <c r="B12" t="str">
+        <v>6.664820102741942e-05</v>
+      </c>
       <c r="C12" t="str">
         <v>90</v>
       </c>
@@ -631,14 +634,46 @@
       </c>
       <c r="E12" t="str">
         <v>4</v>
+      </c>
+      <c r="F12" t="str">
+        <v>separate_learnable_mixed_rope</v>
+      </c>
+      <c r="G12" t="str">
+        <v>16200</v>
       </c>
       <c r="H12" t="str">
         <v>1</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>exp10</v>
+      </c>
+      <c r="B13" t="str">
+        <v>7.537475175922737e-05</v>
+      </c>
+      <c r="C13" t="str">
+        <v>90</v>
+      </c>
+      <c r="D13" t="str">
+        <v>4</v>
+      </c>
+      <c r="E13" t="str">
+        <v>4</v>
+      </c>
+      <c r="F13" t="str">
+        <v>separate_learnable_mixed_rope</v>
+      </c>
+      <c r="G13" t="str">
+        <v>1700</v>
+      </c>
+      <c r="H13" t="str">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -671,9 +671,35 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>exp11</v>
+      </c>
+      <c r="B14" t="str">
+        <v>8.209138468373567e-05</v>
+      </c>
+      <c r="C14" t="str">
+        <v>90</v>
+      </c>
+      <c r="D14" t="str">
+        <v>4</v>
+      </c>
+      <c r="E14" t="str">
+        <v>4</v>
+      </c>
+      <c r="F14" t="str">
+        <v>separate_learnable_mixed_rope</v>
+      </c>
+      <c r="G14" t="str">
+        <v>1700</v>
+      </c>
+      <c r="H14" t="str">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -697,9 +697,35 @@
         <v>1</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>exp12</v>
+      </c>
+      <c r="B15" t="str">
+        <v>4.221895869704895e-05</v>
+      </c>
+      <c r="C15" t="str">
+        <v>90</v>
+      </c>
+      <c r="D15" t="str">
+        <v>4</v>
+      </c>
+      <c r="E15" t="str">
+        <v>4</v>
+      </c>
+      <c r="F15" t="str">
+        <v>separate_learnable_mixed_rope</v>
+      </c>
+      <c r="G15" t="str">
+        <v>16200</v>
+      </c>
+      <c r="H15" t="str">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -723,9 +723,35 @@
         <v>1</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>exp13</v>
+      </c>
+      <c r="B16" t="str">
+        <v>4.858022657572292e-05</v>
+      </c>
+      <c r="C16" t="str">
+        <v>90</v>
+      </c>
+      <c r="D16" t="str">
+        <v>4</v>
+      </c>
+      <c r="E16" t="str">
+        <v>4</v>
+      </c>
+      <c r="F16" t="str">
+        <v>separate_learnable_mixed_rope</v>
+      </c>
+      <c r="G16" t="str">
+        <v>16200</v>
+      </c>
+      <c r="H16" t="str">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -749,9 +749,35 @@
         <v>1</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>exp14</v>
+      </c>
+      <c r="B17" t="str">
+        <v xml:space="preserve"> 4.8428195441374555e-05</v>
+      </c>
+      <c r="C17" t="str">
+        <v>90</v>
+      </c>
+      <c r="D17" t="str">
+        <v>4</v>
+      </c>
+      <c r="E17" t="str">
+        <v>4</v>
+      </c>
+      <c r="F17" t="str">
+        <v>separate_learnable_mixed_rope</v>
+      </c>
+      <c r="G17" t="str">
+        <v>11599</v>
+      </c>
+      <c r="H17" t="str">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:H19"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -406,6 +406,21 @@
       <c r="C1" t="str">
         <v>epoch</v>
       </c>
+      <c r="D1" t="str">
+        <v>m</v>
+      </c>
+      <c r="E1" t="str">
+        <v>n</v>
+      </c>
+      <c r="F1" t="str">
+        <v>positionembedding</v>
+      </c>
+      <c r="G1" t="str">
+        <v>显存</v>
+      </c>
+      <c r="H1" t="str">
+        <v>batch</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -414,10 +429,404 @@
       <c r="B2" t="str">
         <v>0.000422360491938889</v>
       </c>
+      <c r="C2" t="str">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>exp1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>0.001614597043953836</v>
+      </c>
+      <c r="C3" t="str">
+        <v>90</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2</v>
+      </c>
+      <c r="F3" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>exp2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>0.0019393311813473701</v>
+      </c>
+      <c r="C4" t="str">
+        <v>90</v>
+      </c>
+      <c r="D4" t="str">
+        <v>1</v>
+      </c>
+      <c r="E4" t="str">
+        <v>1</v>
+      </c>
+      <c r="F4" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>exp3</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2.8530401323223487e-05</v>
+      </c>
+      <c r="C5" t="str">
+        <v>90</v>
+      </c>
+      <c r="D5" t="str">
+        <v>8</v>
+      </c>
+      <c r="E5" t="str">
+        <v>8</v>
+      </c>
+      <c r="F5" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Baseline1</v>
+      </c>
+      <c r="B6" t="str">
+        <v>0.0004074360185768455</v>
+      </c>
+      <c r="C6" t="str">
+        <v>90</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2</v>
+      </c>
+      <c r="F6" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>exp4</v>
+      </c>
+      <c r="B7" t="str">
+        <v>0.0001579983945703134</v>
+      </c>
+      <c r="C7" t="str">
+        <v>90</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2</v>
+      </c>
+      <c r="E7" t="str">
+        <v>2</v>
+      </c>
+      <c r="F7" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>exp5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>6.45554464426823e-05</v>
+      </c>
+      <c r="C8" t="str">
+        <v>90</v>
+      </c>
+      <c r="D8" t="str">
+        <v>4</v>
+      </c>
+      <c r="E8" t="str">
+        <v>4</v>
+      </c>
+      <c r="F8" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>exp6</v>
+      </c>
+      <c r="B9" t="str">
+        <v>0.0002967970503959805</v>
+      </c>
+      <c r="C9" t="str">
+        <v>90</v>
+      </c>
+      <c r="D9" t="str">
+        <v>4</v>
+      </c>
+      <c r="E9" t="str">
+        <v>4</v>
+      </c>
+      <c r="F9" t="str">
+        <v>None</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>exp7</v>
+      </c>
+      <c r="B10" t="str">
+        <v xml:space="preserve"> 6.603846850339323e-05</v>
+      </c>
+      <c r="C10" t="str">
+        <v>90</v>
+      </c>
+      <c r="D10" t="str">
+        <v>4</v>
+      </c>
+      <c r="E10" t="str">
+        <v>4</v>
+      </c>
+      <c r="F10" t="str">
+        <v>leanable_mixed_rope</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>exp8</v>
+      </c>
+      <c r="B11" t="str">
+        <v>6.929560186108574e-05</v>
+      </c>
+      <c r="C11" t="str">
+        <v>90</v>
+      </c>
+      <c r="D11" t="str">
+        <v>4</v>
+      </c>
+      <c r="E11" t="str">
+        <v>4</v>
+      </c>
+      <c r="F11" t="str">
+        <v>emded_learnable_mix_rope</v>
+      </c>
+      <c r="G11" t="str">
+        <v>16200</v>
+      </c>
+      <c r="H11" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>exp9</v>
+      </c>
+      <c r="B12" t="str">
+        <v>6.664820102741942e-05</v>
+      </c>
+      <c r="C12" t="str">
+        <v>90</v>
+      </c>
+      <c r="D12" t="str">
+        <v>4</v>
+      </c>
+      <c r="E12" t="str">
+        <v>4</v>
+      </c>
+      <c r="F12" t="str">
+        <v>separate_learnable_mixed_rope</v>
+      </c>
+      <c r="G12" t="str">
+        <v>16200</v>
+      </c>
+      <c r="H12" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>exp10</v>
+      </c>
+      <c r="B13" t="str">
+        <v>7.537475175922737e-05</v>
+      </c>
+      <c r="C13" t="str">
+        <v>90</v>
+      </c>
+      <c r="D13" t="str">
+        <v>4</v>
+      </c>
+      <c r="E13" t="str">
+        <v>4</v>
+      </c>
+      <c r="F13" t="str">
+        <v>separate_learnable_mixed_rope</v>
+      </c>
+      <c r="G13" t="str">
+        <v>1700</v>
+      </c>
+      <c r="H13" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>exp11</v>
+      </c>
+      <c r="B14" t="str">
+        <v>8.209138468373567e-05</v>
+      </c>
+      <c r="C14" t="str">
+        <v>90</v>
+      </c>
+      <c r="D14" t="str">
+        <v>4</v>
+      </c>
+      <c r="E14" t="str">
+        <v>4</v>
+      </c>
+      <c r="F14" t="str">
+        <v>separate_learnable_mixed_rope</v>
+      </c>
+      <c r="G14" t="str">
+        <v>1700</v>
+      </c>
+      <c r="H14" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>exp12</v>
+      </c>
+      <c r="B15" t="str">
+        <v>4.221895869704895e-05</v>
+      </c>
+      <c r="C15" t="str">
+        <v>90</v>
+      </c>
+      <c r="D15" t="str">
+        <v>4</v>
+      </c>
+      <c r="E15" t="str">
+        <v>4</v>
+      </c>
+      <c r="F15" t="str">
+        <v>separate_learnable_mixed_rope</v>
+      </c>
+      <c r="G15" t="str">
+        <v>16200</v>
+      </c>
+      <c r="H15" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>exp13</v>
+      </c>
+      <c r="B16" t="str">
+        <v>4.858022657572292e-05</v>
+      </c>
+      <c r="C16" t="str">
+        <v>90</v>
+      </c>
+      <c r="D16" t="str">
+        <v>4</v>
+      </c>
+      <c r="E16" t="str">
+        <v>4</v>
+      </c>
+      <c r="F16" t="str">
+        <v>separate_learnable_mixed_rope</v>
+      </c>
+      <c r="G16" t="str">
+        <v>16200</v>
+      </c>
+      <c r="H16" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>exp14</v>
+      </c>
+      <c r="B17" t="str">
+        <v xml:space="preserve"> 4.8428195441374555e-05</v>
+      </c>
+      <c r="C17" t="str">
+        <v>90</v>
+      </c>
+      <c r="D17" t="str">
+        <v>4</v>
+      </c>
+      <c r="E17" t="str">
+        <v>4</v>
+      </c>
+      <c r="F17" t="str">
+        <v>separate_learnable_mixed_rope</v>
+      </c>
+      <c r="G17" t="str">
+        <v>11599</v>
+      </c>
+      <c r="H17" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Baseline3</v>
+      </c>
+      <c r="B18" t="str">
+        <v>3.5907629353459924e-05</v>
+      </c>
+      <c r="C18" t="str">
+        <v>-</v>
+      </c>
+      <c r="D18" t="str">
+        <v>-</v>
+      </c>
+      <c r="E18" t="str">
+        <v>-</v>
+      </c>
+      <c r="F18" t="str">
+        <v>-</v>
+      </c>
+      <c r="G18" t="str">
+        <v>15448</v>
+      </c>
+      <c r="H18" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Baseline3</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2.1793448468088172e-05</v>
+      </c>
+      <c r="C19" t="str">
+        <v>-</v>
+      </c>
+      <c r="D19" t="str">
+        <v>-</v>
+      </c>
+      <c r="E19" t="str">
+        <v>-</v>
+      </c>
+      <c r="F19" t="str">
+        <v>-</v>
+      </c>
+      <c r="H19" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -775,9 +775,35 @@
         <v>1</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>exp15</v>
+      </c>
+      <c r="B18" t="str">
+        <v>6.81032906868495e-05</v>
+      </c>
+      <c r="C18" t="str">
+        <v>90</v>
+      </c>
+      <c r="D18" t="str">
+        <v>8</v>
+      </c>
+      <c r="E18" t="str">
+        <v>8</v>
+      </c>
+      <c r="F18" t="str">
+        <v>separate_learnable_mixed_rope</v>
+      </c>
+      <c r="G18" t="str">
+        <v>11599</v>
+      </c>
+      <c r="H18" t="str">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -421,6 +421,9 @@
       <c r="H1" t="str">
         <v>batch</v>
       </c>
+      <c r="I1" t="str">
+        <v>num_head</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -800,10 +803,13 @@
       <c r="H18" t="str">
         <v>1</v>
       </c>
+      <c r="I18" t="str">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I18"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -807,9 +807,38 @@
         <v>16</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>exp16</v>
+      </c>
+      <c r="B19" t="str">
+        <v>1.2037563465128187e-05</v>
+      </c>
+      <c r="C19" t="str">
+        <v>90</v>
+      </c>
+      <c r="D19" t="str">
+        <v>256</v>
+      </c>
+      <c r="E19" t="str">
+        <v>256</v>
+      </c>
+      <c r="F19" t="str">
+        <v>relative_position</v>
+      </c>
+      <c r="G19" t="str">
+        <v>12566</v>
+      </c>
+      <c r="H19" t="str">
+        <v>1</v>
+      </c>
+      <c r="I19" t="str">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/comparison.xlsx
+++ b/comparison.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="str">
@@ -836,9 +836,38 @@
         <v>1</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>exp17</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2.853369733202271e-05</v>
+      </c>
+      <c r="C20" t="str">
+        <v>90</v>
+      </c>
+      <c r="D20" t="str">
+        <v>128</v>
+      </c>
+      <c r="E20" t="str">
+        <v>128</v>
+      </c>
+      <c r="F20" t="str">
+        <v>relative_position</v>
+      </c>
+      <c r="G20" t="str">
+        <v>12517</v>
+      </c>
+      <c r="H20" t="str">
+        <v>1</v>
+      </c>
+      <c r="I20" t="str">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I20"/>
   </ignoredErrors>
 </worksheet>
 </file>